--- a/data-manipulation-scripts/sheets-cleanup/sheets/DUTO AR 08_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/DUTO AR 08_02.xlsx
@@ -358,7 +358,9 @@
       <c r="C2" s="2">
         <v>2.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -398,7 +400,9 @@
       <c r="C5" s="2">
         <v>2.0</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -408,7 +412,9 @@
         <v>13</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4"/>
